--- a/Totales Generales20232.xlsx
+++ b/Totales Generales20232.xlsx
@@ -608,31 +608,31 @@
         <v>3</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H2">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I2">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="J2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K2">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="L2">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="M2" s="1">
-        <v>74</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -655,13 +655,13 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H3">
         <v>6</v>
       </c>
       <c r="I3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J3">
         <v>40</v>
@@ -702,19 +702,19 @@
         <v>8</v>
       </c>
       <c r="I4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J4">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K4">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="L4">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M4" s="1">
-        <v>23.5</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -731,31 +731,31 @@
         <v>5</v>
       </c>
       <c r="E5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H5">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I5">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="J5">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K5">
-        <v>340</v>
+        <v>367</v>
       </c>
       <c r="L5">
-        <v>259</v>
+        <v>232</v>
       </c>
       <c r="M5" s="1">
-        <v>43.2</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -933,31 +933,31 @@
         <v>10</v>
       </c>
       <c r="E10">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F10">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G10">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H10">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="I10">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="J10">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K10">
-        <v>505</v>
+        <v>532</v>
       </c>
       <c r="L10">
-        <v>465</v>
+        <v>438</v>
       </c>
       <c r="M10" s="1">
-        <v>47.9</v>
+        <v>45.2</v>
       </c>
     </row>
   </sheetData>
@@ -1025,34 +1025,34 @@
         <v>192</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L2">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="M2" s="1">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1066,34 +1066,34 @@
         <v>220</v>
       </c>
       <c r="D3">
-        <v>175</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="L3">
-        <v>220</v>
+        <v>60</v>
       </c>
       <c r="M3" s="1">
-        <v>100</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1110,31 +1110,31 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>187</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="L4">
-        <v>187</v>
+        <v>66</v>
       </c>
       <c r="M4" s="1">
-        <v>100</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1148,34 +1148,34 @@
         <v>599</v>
       </c>
       <c r="D5">
-        <v>175</v>
+        <v>10</v>
       </c>
       <c r="E5">
-        <v>232</v>
+        <v>15</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>299</v>
       </c>
       <c r="L5">
-        <v>599</v>
+        <v>300</v>
       </c>
       <c r="M5" s="1">
-        <v>100</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1189,34 +1189,34 @@
         <v>128</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="L6">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="M6" s="1">
-        <v>100</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1230,34 +1230,34 @@
         <v>130</v>
       </c>
       <c r="D7">
-        <v>73</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="L7">
-        <v>130</v>
+        <v>46</v>
       </c>
       <c r="M7" s="1">
-        <v>100</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1274,31 +1274,31 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>112</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="L8">
-        <v>113</v>
+        <v>45</v>
       </c>
       <c r="M8" s="1">
-        <v>100</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1312,34 +1312,34 @@
         <v>371</v>
       </c>
       <c r="D9">
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="E9">
-        <v>168</v>
+        <v>13</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="I9">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="L9">
-        <v>371</v>
+        <v>177</v>
       </c>
       <c r="M9" s="1">
-        <v>100</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1350,34 +1350,34 @@
         <v>970</v>
       </c>
       <c r="D10">
-        <v>248</v>
+        <v>20</v>
       </c>
       <c r="E10">
-        <v>400</v>
+        <v>28</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="I10">
-        <v>2</v>
+        <v>107</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>493</v>
       </c>
       <c r="L10">
-        <v>970</v>
+        <v>477</v>
       </c>
       <c r="M10" s="1">
-        <v>100</v>
+        <v>49.2</v>
       </c>
     </row>
   </sheetData>
@@ -1445,25 +1445,25 @@
         <v>192</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2">
         <v>11</v>
       </c>
-      <c r="F2">
+      <c r="G2">
+        <v>10</v>
+      </c>
+      <c r="H2">
         <v>15</v>
       </c>
-      <c r="G2">
-        <v>14</v>
-      </c>
-      <c r="H2">
-        <v>42</v>
-      </c>
       <c r="I2">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J2">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -1492,28 +1492,28 @@
         <v>3</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J3">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="K3">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="L3">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="M3" s="1">
-        <v>33.2</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1539,22 +1539,22 @@
         <v>4</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J4">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="K4">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="L4">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="M4" s="1">
-        <v>23.5</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1568,34 +1568,34 @@
         <v>599</v>
       </c>
       <c r="D5">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E5">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G5">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H5">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="I5">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J5">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="K5">
-        <v>290</v>
+        <v>311</v>
       </c>
       <c r="L5">
-        <v>309</v>
+        <v>288</v>
       </c>
       <c r="M5" s="1">
-        <v>51.6</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1609,25 +1609,25 @@
         <v>128</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>18</v>
+      </c>
+      <c r="H6">
         <v>13</v>
       </c>
-      <c r="G6">
-        <v>22</v>
-      </c>
-      <c r="H6">
-        <v>15</v>
-      </c>
       <c r="I6">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J6">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -1650,34 +1650,34 @@
         <v>130</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G7">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="K7">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="L7">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="M7" s="1">
-        <v>49.2</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1694,31 +1694,31 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H8">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J8">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="K8">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L8">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M8" s="1">
-        <v>38.1</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1732,34 +1732,34 @@
         <v>371</v>
       </c>
       <c r="D9">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E9">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F9">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G9">
+        <v>27</v>
+      </c>
+      <c r="H9">
+        <v>28</v>
+      </c>
+      <c r="I9">
         <v>33</v>
       </c>
-      <c r="H9">
-        <v>31</v>
-      </c>
-      <c r="I9">
-        <v>32</v>
-      </c>
       <c r="J9">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K9">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="L9">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="M9" s="1">
-        <v>63.1</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1773,31 +1773,31 @@
         <v>28</v>
       </c>
       <c r="E10">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F10">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G10">
+        <v>45</v>
+      </c>
+      <c r="H10">
         <v>56</v>
       </c>
-      <c r="H10">
-        <v>87</v>
-      </c>
       <c r="I10">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="J10">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="K10">
-        <v>427</v>
+        <v>465</v>
       </c>
       <c r="L10">
-        <v>543</v>
+        <v>505</v>
       </c>
       <c r="M10" s="1">
-        <v>56</v>
+        <v>52.1</v>
       </c>
     </row>
   </sheetData>
@@ -1859,10 +1859,10 @@
         <v>25</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -1874,7 +1874,7 @@
         <v>2</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2">
         <v>10</v>
@@ -1897,10 +1897,10 @@
         <v>39</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -1909,13 +1909,13 @@
         <v>2</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1938,22 +1938,22 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I4">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1976,19 +1976,19 @@
         <v>2</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2011,25 +2011,25 @@
         <v>24</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2049,25 +2049,25 @@
         <v>38</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
         <v>6</v>
       </c>
-      <c r="G7">
-        <v>22</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
       <c r="I7">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2093,28 +2093,28 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8">
         <v>2</v>
       </c>
       <c r="H8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K8">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L8" s="1">
-        <v>51.7</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -2137,13 +2137,13 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J9">
         <v>37</v>
@@ -2166,31 +2166,31 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I10">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J10">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="K10">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="L10" s="1">
-        <v>45.7</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2204,31 +2204,31 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11">
         <v>2</v>
       </c>
       <c r="H11">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I11">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J11">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K11">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L11" s="1">
-        <v>44.4</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -2248,25 +2248,25 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J12">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K12">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L12" s="1">
-        <v>41.9</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -2280,31 +2280,31 @@
         <v>1</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13">
         <v>1</v>
       </c>
       <c r="J13">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L13" s="1">
-        <v>10.5</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -2324,7 +2324,7 @@
         <v>1</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -2333,16 +2333,16 @@
         <v>3</v>
       </c>
       <c r="I14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L14" s="1">
-        <v>40</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -2368,19 +2368,19 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="K15">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L15" s="1">
-        <v>16.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -2400,25 +2400,25 @@
         <v>0</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16">
         <v>1</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K16">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L16" s="1">
-        <v>12.5</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -2447,16 +2447,16 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J17">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L17" s="1">
-        <v>6.5</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -2479,10 +2479,10 @@
         <v>2</v>
       </c>
       <c r="G18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I18">
         <v>3</v>
@@ -2517,22 +2517,22 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J19">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K19">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L19" s="1">
-        <v>24.3</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -2543,25 +2543,25 @@
         <v>30</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E20">
+        <v>3</v>
+      </c>
+      <c r="F20">
         <v>5</v>
       </c>
-      <c r="F20">
+      <c r="G20">
+        <v>3</v>
+      </c>
+      <c r="H20">
+        <v>3</v>
+      </c>
+      <c r="I20">
         <v>8</v>
-      </c>
-      <c r="G20">
-        <v>2</v>
-      </c>
-      <c r="H20">
-        <v>3</v>
-      </c>
-      <c r="I20">
-        <v>5</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -2581,25 +2581,25 @@
         <v>29</v>
       </c>
       <c r="C21">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E21">
+        <v>2</v>
+      </c>
+      <c r="F21">
+        <v>4</v>
+      </c>
+      <c r="G21">
         <v>5</v>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>5</v>
       </c>
-      <c r="G21">
+      <c r="I21">
         <v>4</v>
-      </c>
-      <c r="H21">
-        <v>2</v>
-      </c>
-      <c r="I21">
-        <v>3</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -2619,25 +2619,25 @@
         <v>23</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I22">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -2657,25 +2657,25 @@
         <v>34</v>
       </c>
       <c r="C23">
+        <v>3</v>
+      </c>
+      <c r="D23">
+        <v>3</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23">
         <v>4</v>
       </c>
-      <c r="D23">
-        <v>3</v>
-      </c>
-      <c r="E23">
-        <v>2</v>
-      </c>
-      <c r="F23">
-        <v>5</v>
-      </c>
       <c r="G23">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H23">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I23">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -2698,19 +2698,19 @@
         <v>1</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24">
         <v>0</v>
       </c>
       <c r="F24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24">
         <v>4</v>
@@ -2736,31 +2736,31 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G25">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H25">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J25">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K25">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L25" s="1">
-        <v>78.3</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -2771,34 +2771,34 @@
         <v>31</v>
       </c>
       <c r="C26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F26">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H26">
         <v>2</v>
       </c>
       <c r="I26">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J26">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K26">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="L26" s="1">
-        <v>71</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27">
         <v>2</v>
@@ -2824,19 +2824,19 @@
         <v>2</v>
       </c>
       <c r="H27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J27">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K27">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L27" s="1">
-        <v>52.4</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -2859,22 +2859,22 @@
         <v>0</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K28">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L28" s="1">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -2894,25 +2894,25 @@
         <v>0</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29">
         <v>0</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I29">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J29">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K29">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L29" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -2929,7 +2929,7 @@
         <v>0</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -2941,7 +2941,7 @@
         <v>4</v>
       </c>
       <c r="I30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J30">
         <v>11</v>
@@ -2964,31 +2964,31 @@
         <v>0</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F31">
         <v>2</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H31">
         <v>1</v>
       </c>
       <c r="I31">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J31">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K31">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L31" s="1">
-        <v>40.6</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -3011,7 +3011,7 @@
         <v>0</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -3020,13 +3020,13 @@
         <v>1</v>
       </c>
       <c r="J32">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L32" s="1">
-        <v>20</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -3043,28 +3043,28 @@
         <v>0</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33">
         <v>1</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I33">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J33">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K33">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L33" s="1">
-        <v>23.1</v>
+        <v>34.6</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -3081,28 +3081,28 @@
         <v>1</v>
       </c>
       <c r="E34">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G34">
         <v>0</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34">
         <v>1</v>
       </c>
       <c r="J34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L34" s="1">
-        <v>42.9</v>
+        <v>35.7</v>
       </c>
     </row>
   </sheetData>
@@ -3204,19 +3204,19 @@
         <v>31</v>
       </c>
       <c r="C4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4" s="1">
-        <v>38.7</v>
+        <v>41.9</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>58.1</v>
       </c>
       <c r="H4" s="1">
         <v>0</v>
@@ -3282,7 +3282,7 @@
         <v>38</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -3291,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="1">
-        <v>0</v>
+        <v>60.5</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -3311,19 +3311,19 @@
         <v>14</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E8">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F8" s="1">
         <v>48.3</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>55.2</v>
       </c>
       <c r="H8" s="1">
-        <v>48.3</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -3337,7 +3337,7 @@
         <v>37</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="E9">
         <v>37</v>
@@ -3346,7 +3346,7 @@
         <v>88.09999999999999</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="H9" s="1">
         <v>88.09999999999999</v>
@@ -3363,19 +3363,19 @@
         <v>19</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E10">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F10" s="1">
         <v>54.3</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>54.3</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -3389,19 +3389,19 @@
         <v>25</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E11">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F11" s="1">
         <v>55.6</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>62.2</v>
       </c>
       <c r="H11" s="1">
-        <v>55.6</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -3415,19 +3415,19 @@
         <v>18</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E12">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F12" s="1">
         <v>58.1</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>61.3</v>
       </c>
       <c r="H12" s="1">
-        <v>58.1</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -3441,19 +3441,19 @@
         <v>34</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="E13">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F13" s="1">
         <v>89.5</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H13" s="1">
-        <v>89.5</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -3467,19 +3467,19 @@
         <v>18</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F14" s="1">
         <v>60</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>63.3</v>
       </c>
       <c r="H14" s="1">
-        <v>60</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -3490,22 +3490,22 @@
         <v>37</v>
       </c>
       <c r="C15">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="E15">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F15" s="1">
-        <v>83.8</v>
+        <v>86.5</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>83.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -3519,19 +3519,19 @@
         <v>21</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E16">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F16" s="1">
         <v>87.5</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>79.2</v>
       </c>
       <c r="H16" s="1">
-        <v>87.5</v>
+        <v>79.2</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -3548,7 +3548,7 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F17" s="1">
         <v>93.5</v>
@@ -3557,7 +3557,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>93.5</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -3571,7 +3571,7 @@
         <v>16</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E18">
         <v>16</v>
@@ -3580,7 +3580,7 @@
         <v>57.1</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>57.1</v>
       </c>
       <c r="H18" s="1">
         <v>57.1</v>
@@ -3594,22 +3594,22 @@
         <v>37</v>
       </c>
       <c r="C19">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E19">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F19" s="1">
-        <v>75.7</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="H19" s="1">
-        <v>75.7</v>
+        <v>81.09999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -3623,7 +3623,7 @@
         <v>5</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -3632,7 +3632,7 @@
         <v>16.7</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>26.7</v>
       </c>
       <c r="H20" s="1">
         <v>0</v>
@@ -3649,7 +3649,7 @@
         <v>3</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -3658,7 +3658,7 @@
         <v>10.3</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>13.8</v>
       </c>
       <c r="H21" s="1">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>8</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>34.8</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>52.2</v>
       </c>
       <c r="H22" s="1">
         <v>0</v>
@@ -3701,7 +3701,7 @@
         <v>9</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -3710,7 +3710,7 @@
         <v>26.5</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>41.2</v>
       </c>
       <c r="H23" s="1">
         <v>2.9</v>
@@ -3727,7 +3727,7 @@
         <v>4</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -3736,7 +3736,7 @@
         <v>33.3</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="H24" s="1">
         <v>0</v>
@@ -3753,19 +3753,19 @@
         <v>5</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E25">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F25" s="1">
         <v>21.7</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>39.1</v>
       </c>
       <c r="H25" s="1">
-        <v>21.7</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -3779,19 +3779,19 @@
         <v>9</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E26">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F26" s="1">
         <v>29</v>
       </c>
       <c r="G26" s="1">
-        <v>0</v>
+        <v>48.4</v>
       </c>
       <c r="H26" s="1">
-        <v>29</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -3805,19 +3805,19 @@
         <v>10</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E27">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F27" s="1">
         <v>47.6</v>
       </c>
       <c r="G27" s="1">
-        <v>0</v>
+        <v>61.9</v>
       </c>
       <c r="H27" s="1">
-        <v>47.6</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -3831,19 +3831,19 @@
         <v>21</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E28">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F28" s="1">
         <v>84</v>
       </c>
       <c r="G28" s="1">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="H28" s="1">
-        <v>84</v>
+        <v>92</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -3857,19 +3857,19 @@
         <v>21</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E29">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F29" s="1">
         <v>70</v>
       </c>
       <c r="G29" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H29" s="1">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -3883,7 +3883,7 @@
         <v>11</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E30">
         <v>11</v>
@@ -3892,7 +3892,7 @@
         <v>42.3</v>
       </c>
       <c r="G30" s="1">
-        <v>0</v>
+        <v>42.3</v>
       </c>
       <c r="H30" s="1">
         <v>42.3</v>
@@ -3909,19 +3909,19 @@
         <v>19</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E31">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F31" s="1">
         <v>59.4</v>
       </c>
       <c r="G31" s="1">
-        <v>0</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H31" s="1">
-        <v>59.4</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -3935,19 +3935,19 @@
         <v>12</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E32">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F32" s="1">
         <v>80</v>
       </c>
       <c r="G32" s="1">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="H32" s="1">
-        <v>80</v>
+        <v>73.3</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -3961,19 +3961,19 @@
         <v>20</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E33">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F33" s="1">
         <v>76.90000000000001</v>
       </c>
       <c r="G33" s="1">
-        <v>0</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="H33" s="1">
-        <v>76.90000000000001</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -3987,19 +3987,19 @@
         <v>8</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F34" s="1">
         <v>57.1</v>
       </c>
       <c r="G34" s="1">
-        <v>0</v>
+        <v>57.1</v>
       </c>
       <c r="H34" s="1">
-        <v>57.1</v>
+        <v>64.3</v>
       </c>
     </row>
   </sheetData>

--- a/Totales Generales20232.xlsx
+++ b/Totales Generales20232.xlsx
@@ -608,31 +608,31 @@
         <v>3</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J2">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="K2">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="L2">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="M2" s="1">
-        <v>61.5</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -731,31 +731,31 @@
         <v>5</v>
       </c>
       <c r="E5">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G5">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H5">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I5">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="J5">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K5">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="L5">
-        <v>232</v>
+        <v>213</v>
       </c>
       <c r="M5" s="1">
-        <v>38.7</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -933,31 +933,31 @@
         <v>10</v>
       </c>
       <c r="E10">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F10">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G10">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H10">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I10">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="J10">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="K10">
-        <v>532</v>
+        <v>551</v>
       </c>
       <c r="L10">
-        <v>438</v>
+        <v>419</v>
       </c>
       <c r="M10" s="1">
-        <v>45.2</v>
+        <v>43.2</v>
       </c>
     </row>
   </sheetData>
@@ -1025,34 +1025,34 @@
         <v>192</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E2">
         <v>10</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H2">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I2">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="J2">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="K2">
-        <v>18</v>
+        <v>108</v>
       </c>
       <c r="L2">
-        <v>174</v>
+        <v>84</v>
       </c>
       <c r="M2" s="1">
-        <v>90.59999999999999</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1122,19 +1122,19 @@
         <v>6</v>
       </c>
       <c r="I4">
+        <v>11</v>
+      </c>
+      <c r="J4">
         <v>12</v>
       </c>
-      <c r="J4">
-        <v>41</v>
-      </c>
       <c r="K4">
-        <v>121</v>
+        <v>151</v>
       </c>
       <c r="L4">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="M4" s="1">
-        <v>35.3</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1148,34 +1148,34 @@
         <v>599</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E5">
         <v>15</v>
       </c>
       <c r="F5">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G5">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H5">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="I5">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="J5">
-        <v>125</v>
+        <v>56</v>
       </c>
       <c r="K5">
-        <v>299</v>
+        <v>419</v>
       </c>
       <c r="L5">
-        <v>300</v>
+        <v>180</v>
       </c>
       <c r="M5" s="1">
-        <v>50.1</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1350,34 +1350,34 @@
         <v>970</v>
       </c>
       <c r="D10">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E10">
         <v>28</v>
       </c>
       <c r="F10">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G10">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H10">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="I10">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="J10">
-        <v>168</v>
+        <v>99</v>
       </c>
       <c r="K10">
-        <v>493</v>
+        <v>613</v>
       </c>
       <c r="L10">
-        <v>477</v>
+        <v>357</v>
       </c>
       <c r="M10" s="1">
-        <v>49.2</v>
+        <v>36.8</v>
       </c>
     </row>
   </sheetData>
@@ -1445,25 +1445,25 @@
         <v>192</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I2">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="J2">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -1568,25 +1568,25 @@
         <v>599</v>
       </c>
       <c r="D5">
+        <v>12</v>
+      </c>
+      <c r="E5">
+        <v>8</v>
+      </c>
+      <c r="F5">
         <v>14</v>
       </c>
-      <c r="E5">
-        <v>9</v>
-      </c>
-      <c r="F5">
-        <v>15</v>
-      </c>
       <c r="G5">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H5">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I5">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="J5">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="K5">
         <v>311</v>
@@ -1770,25 +1770,25 @@
         <v>970</v>
       </c>
       <c r="D10">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E10">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F10">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G10">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H10">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I10">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="J10">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="K10">
         <v>465</v>
@@ -1859,10 +1859,10 @@
         <v>25</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -1897,7 +1897,7 @@
         <v>39</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1973,25 +1973,25 @@
         <v>35</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
         <v>4</v>
       </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
       <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
         <v>21</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2011,19 +2011,19 @@
         <v>24</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6">
         <v>6</v>
@@ -2052,22 +2052,22 @@
         <v>2</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>2</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I7">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -3155,7 +3155,7 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -3164,7 +3164,7 @@
         <v>40</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H2" s="1">
         <v>0</v>
@@ -3181,7 +3181,7 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -3190,7 +3190,7 @@
         <v>51.3</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>53.8</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
@@ -3230,19 +3230,19 @@
         <v>35</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5" s="1">
-        <v>0</v>
+        <v>54.3</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
@@ -3259,7 +3259,7 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -3268,7 +3268,7 @@
         <v>33.3</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>45.8</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
@@ -3285,7 +3285,7 @@
         <v>23</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -3294,7 +3294,7 @@
         <v>60.5</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
@@ -3545,7 +3545,7 @@
         <v>29</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E17">
         <v>30</v>
@@ -3554,7 +3554,7 @@
         <v>93.5</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="H17" s="1">
         <v>96.8</v>

--- a/Totales Generales20232.xlsx
+++ b/Totales Generales20232.xlsx
@@ -684,7 +684,7 @@
         <v>14</v>
       </c>
       <c r="C4">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -708,13 +708,13 @@
         <v>17</v>
       </c>
       <c r="K4">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="L4">
         <v>41</v>
       </c>
       <c r="M4" s="1">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -725,7 +725,7 @@
         <v>14</v>
       </c>
       <c r="C5">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="D5">
         <v>5</v>
@@ -749,13 +749,13 @@
         <v>82</v>
       </c>
       <c r="K5">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="L5">
         <v>213</v>
       </c>
       <c r="M5" s="1">
-        <v>35.6</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -848,7 +848,7 @@
         <v>15</v>
       </c>
       <c r="C8">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -872,13 +872,13 @@
         <v>19</v>
       </c>
       <c r="K8">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L8">
         <v>43</v>
       </c>
       <c r="M8" s="1">
-        <v>38.1</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -889,7 +889,7 @@
         <v>15</v>
       </c>
       <c r="C9">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D9">
         <v>5</v>
@@ -913,13 +913,13 @@
         <v>59</v>
       </c>
       <c r="K9">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L9">
         <v>206</v>
       </c>
       <c r="M9" s="1">
-        <v>55.5</v>
+        <v>55.4</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -927,7 +927,7 @@
         <v>13</v>
       </c>
       <c r="C10">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="D10">
         <v>10</v>
@@ -951,13 +951,13 @@
         <v>141</v>
       </c>
       <c r="K10">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="L10">
         <v>419</v>
       </c>
       <c r="M10" s="1">
-        <v>43.2</v>
+        <v>43.1</v>
       </c>
     </row>
   </sheetData>
@@ -1037,10 +1037,10 @@
         <v>10</v>
       </c>
       <c r="H2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J2">
         <v>21</v>
@@ -1104,7 +1104,7 @@
         <v>14</v>
       </c>
       <c r="C4">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1128,13 +1128,13 @@
         <v>12</v>
       </c>
       <c r="K4">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="L4">
         <v>36</v>
       </c>
       <c r="M4" s="1">
-        <v>19.3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1145,7 +1145,7 @@
         <v>14</v>
       </c>
       <c r="C5">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="D5">
         <v>6</v>
@@ -1160,22 +1160,22 @@
         <v>18</v>
       </c>
       <c r="H5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I5">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J5">
         <v>56</v>
       </c>
       <c r="K5">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="L5">
         <v>180</v>
       </c>
       <c r="M5" s="1">
-        <v>30.1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1268,7 +1268,7 @@
         <v>15</v>
       </c>
       <c r="C8">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -1289,16 +1289,16 @@
         <v>10</v>
       </c>
       <c r="J8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K8">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L8">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M8" s="1">
-        <v>39.8</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1309,7 +1309,7 @@
         <v>15</v>
       </c>
       <c r="C9">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D9">
         <v>10</v>
@@ -1330,16 +1330,16 @@
         <v>32</v>
       </c>
       <c r="J9">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K9">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L9">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M9" s="1">
-        <v>47.7</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1347,7 +1347,7 @@
         <v>13</v>
       </c>
       <c r="C10">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="D10">
         <v>16</v>
@@ -1362,22 +1362,22 @@
         <v>35</v>
       </c>
       <c r="H10">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I10">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J10">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K10">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="L10">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="M10" s="1">
-        <v>36.8</v>
+        <v>36.6</v>
       </c>
     </row>
   </sheetData>
@@ -1445,25 +1445,25 @@
         <v>192</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2">
         <v>3</v>
       </c>
-      <c r="F2">
-        <v>10</v>
-      </c>
       <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
         <v>8</v>
-      </c>
-      <c r="H2">
-        <v>17</v>
       </c>
       <c r="I2">
         <v>21</v>
       </c>
       <c r="J2">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -1486,34 +1486,34 @@
         <v>220</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I3">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J3">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="K3">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L3">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M3" s="1">
-        <v>27.3</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1524,7 +1524,7 @@
         <v>14</v>
       </c>
       <c r="C4">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1533,28 +1533,28 @@
         <v>2</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>6</v>
+      </c>
+      <c r="J4">
         <v>4</v>
       </c>
-      <c r="H4">
-        <v>6</v>
-      </c>
-      <c r="I4">
-        <v>11</v>
-      </c>
-      <c r="J4">
-        <v>12</v>
-      </c>
       <c r="K4">
-        <v>151</v>
+        <v>176</v>
       </c>
       <c r="L4">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="M4" s="1">
-        <v>19.3</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1565,37 +1565,37 @@
         <v>14</v>
       </c>
       <c r="C5">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="D5">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5">
         <v>14</v>
       </c>
-      <c r="G5">
-        <v>16</v>
-      </c>
-      <c r="H5">
-        <v>30</v>
-      </c>
       <c r="I5">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="J5">
-        <v>143</v>
+        <v>184</v>
       </c>
       <c r="K5">
-        <v>311</v>
+        <v>335</v>
       </c>
       <c r="L5">
-        <v>288</v>
+        <v>266</v>
       </c>
       <c r="M5" s="1">
-        <v>48.1</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1609,25 +1609,25 @@
         <v>128</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
         <v>10</v>
-      </c>
-      <c r="F6">
-        <v>8</v>
-      </c>
-      <c r="G6">
-        <v>18</v>
       </c>
       <c r="H6">
         <v>13</v>
       </c>
       <c r="I6">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="J6">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -1653,31 +1653,31 @@
         <v>2</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
         <v>7</v>
       </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-      <c r="H7">
-        <v>7</v>
-      </c>
-      <c r="I7">
-        <v>10</v>
-      </c>
       <c r="J7">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K7">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="L7">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="M7" s="1">
-        <v>35.4</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1688,7 +1688,7 @@
         <v>15</v>
       </c>
       <c r="C8">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -1697,28 +1697,28 @@
         <v>2</v>
       </c>
       <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>2</v>
+      </c>
+      <c r="I8">
         <v>4</v>
-      </c>
-      <c r="G8">
-        <v>7</v>
-      </c>
-      <c r="H8">
-        <v>8</v>
-      </c>
-      <c r="I8">
-        <v>10</v>
       </c>
       <c r="J8">
         <v>13</v>
       </c>
       <c r="K8">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="L8">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="M8" s="1">
-        <v>38.9</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1729,37 +1729,37 @@
         <v>15</v>
       </c>
       <c r="C9">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D9">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E9">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F9">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="G9">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="H9">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="I9">
         <v>33</v>
       </c>
       <c r="J9">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="K9">
-        <v>154</v>
+        <v>189</v>
       </c>
       <c r="L9">
-        <v>217</v>
+        <v>183</v>
       </c>
       <c r="M9" s="1">
-        <v>58.5</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1767,37 +1767,37 @@
         <v>13</v>
       </c>
       <c r="C10">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="D10">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E10">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F10">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="G10">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="H10">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="I10">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="J10">
-        <v>213</v>
+        <v>278</v>
       </c>
       <c r="K10">
-        <v>465</v>
+        <v>524</v>
       </c>
       <c r="L10">
-        <v>505</v>
+        <v>449</v>
       </c>
       <c r="M10" s="1">
-        <v>52.1</v>
+        <v>46.1</v>
       </c>
     </row>
   </sheetData>
@@ -1859,25 +1859,25 @@
         <v>25</v>
       </c>
       <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
         <v>5</v>
       </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
       <c r="I2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1900,22 +1900,22 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1935,10 +1935,10 @@
         <v>31</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1947,13 +1947,13 @@
         <v>1</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H4">
         <v>3</v>
       </c>
       <c r="I4">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1973,25 +1973,25 @@
         <v>35</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2011,25 +2011,25 @@
         <v>24</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I6">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2049,25 +2049,25 @@
         <v>38</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I7">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -2102,19 +2102,19 @@
         <v>2</v>
       </c>
       <c r="H8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I8">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="J8">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="K8">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="L8" s="1">
-        <v>44.8</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -2137,7 +2137,7 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -2146,13 +2146,13 @@
         <v>3</v>
       </c>
       <c r="J9">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L9" s="1">
-        <v>11.9</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -2169,7 +2169,7 @@
         <v>1</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -2178,19 +2178,19 @@
         <v>0</v>
       </c>
       <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>4</v>
+      </c>
+      <c r="J10">
+        <v>29</v>
+      </c>
+      <c r="K10">
         <v>6</v>
       </c>
-      <c r="I10">
-        <v>1</v>
-      </c>
-      <c r="J10">
-        <v>25</v>
-      </c>
-      <c r="K10">
-        <v>10</v>
-      </c>
       <c r="L10" s="1">
-        <v>28.6</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2204,7 +2204,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -2213,22 +2213,22 @@
         <v>1</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I11">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J11">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K11">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L11" s="1">
-        <v>37.8</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -2245,28 +2245,28 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H12">
         <v>2</v>
       </c>
       <c r="I12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J12">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K12">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L12" s="1">
-        <v>38.7</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -2277,10 +2277,10 @@
         <v>38</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -2295,16 +2295,16 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L13" s="1">
-        <v>7.9</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -2321,28 +2321,28 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J14">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="K14">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L14" s="1">
-        <v>36.7</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -2403,22 +2403,22 @@
         <v>0</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J16">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K16">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L16" s="1">
-        <v>20.8</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -2426,7 +2426,7 @@
         <v>32</v>
       </c>
       <c r="B17">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -2447,16 +2447,16 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="1">
-        <v>3.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -2476,25 +2476,25 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J18">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="K18">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L18" s="1">
-        <v>42.9</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -2520,19 +2520,19 @@
         <v>0</v>
       </c>
       <c r="H19">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J19">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K19">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L19" s="1">
-        <v>18.9</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -2543,25 +2543,25 @@
         <v>30</v>
       </c>
       <c r="C20">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F20">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H20">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I20">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -2581,25 +2581,25 @@
         <v>29</v>
       </c>
       <c r="C21">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E21">
         <v>2</v>
       </c>
       <c r="F21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H21">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I21">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -2622,13 +2622,13 @@
         <v>0</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G22">
         <v>2</v>
@@ -2637,7 +2637,7 @@
         <v>1</v>
       </c>
       <c r="I22">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -2657,25 +2657,25 @@
         <v>34</v>
       </c>
       <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
         <v>3</v>
       </c>
-      <c r="D23">
-        <v>3</v>
-      </c>
-      <c r="E23">
-        <v>1</v>
-      </c>
-      <c r="F23">
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
         <v>4</v>
       </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-      <c r="H23">
-        <v>3</v>
-      </c>
       <c r="I23">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -2695,25 +2695,25 @@
         <v>12</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24">
         <v>0</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H24">
         <v>1</v>
       </c>
       <c r="I24">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -2736,31 +2736,31 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25">
         <v>0</v>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H25">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J25">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K25">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L25" s="1">
-        <v>60.9</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -2771,34 +2771,34 @@
         <v>31</v>
       </c>
       <c r="C26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26">
         <v>1</v>
       </c>
       <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26">
         <v>4</v>
       </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
       <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
         <v>3</v>
       </c>
-      <c r="H26">
-        <v>2</v>
-      </c>
       <c r="I26">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J26">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K26">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L26" s="1">
-        <v>51.6</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -2809,34 +2809,34 @@
         <v>21</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J27">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K27">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L27" s="1">
-        <v>38.1</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -2865,16 +2865,16 @@
         <v>0</v>
       </c>
       <c r="I28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L28" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -2900,19 +2900,19 @@
         <v>0</v>
       </c>
       <c r="H29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J29">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L29" s="1">
-        <v>20</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -2929,28 +2929,28 @@
         <v>0</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
         <v>4</v>
       </c>
-      <c r="I30">
-        <v>6</v>
-      </c>
       <c r="J30">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="K30">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="L30" s="1">
-        <v>57.7</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -2967,28 +2967,28 @@
         <v>0</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H31">
         <v>1</v>
       </c>
       <c r="I31">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J31">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K31">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L31" s="1">
-        <v>34.4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -3011,22 +3011,22 @@
         <v>0</v>
       </c>
       <c r="G32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32">
         <v>1</v>
       </c>
       <c r="J32">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L32" s="1">
-        <v>26.7</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -3043,28 +3043,28 @@
         <v>0</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I33">
         <v>2</v>
       </c>
       <c r="J33">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K33">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L33" s="1">
-        <v>34.6</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -3072,7 +3072,7 @@
         <v>49</v>
       </c>
       <c r="B34">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -3084,25 +3084,25 @@
         <v>0</v>
       </c>
       <c r="F34">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K34">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L34" s="1">
-        <v>35.7</v>
+        <v>26.7</v>
       </c>
     </row>
   </sheetData>
@@ -3314,7 +3314,7 @@
         <v>16</v>
       </c>
       <c r="E8">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F8" s="1">
         <v>48.3</v>
@@ -3323,7 +3323,7 @@
         <v>55.2</v>
       </c>
       <c r="H8" s="1">
-        <v>55.2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -3340,7 +3340,7 @@
         <v>37</v>
       </c>
       <c r="E9">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F9" s="1">
         <v>88.09999999999999</v>
@@ -3349,7 +3349,7 @@
         <v>88.09999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>88.09999999999999</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -3366,7 +3366,7 @@
         <v>25</v>
       </c>
       <c r="E10">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F10" s="1">
         <v>54.3</v>
@@ -3375,7 +3375,7 @@
         <v>71.40000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>71.40000000000001</v>
+        <v>82.90000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -3392,7 +3392,7 @@
         <v>28</v>
       </c>
       <c r="E11">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F11" s="1">
         <v>55.6</v>
@@ -3401,7 +3401,7 @@
         <v>62.2</v>
       </c>
       <c r="H11" s="1">
-        <v>62.2</v>
+        <v>68.90000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -3418,7 +3418,7 @@
         <v>19</v>
       </c>
       <c r="E12">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F12" s="1">
         <v>58.1</v>
@@ -3427,7 +3427,7 @@
         <v>61.3</v>
       </c>
       <c r="H12" s="1">
-        <v>61.3</v>
+        <v>77.40000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -3444,7 +3444,7 @@
         <v>35</v>
       </c>
       <c r="E13">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F13" s="1">
         <v>89.5</v>
@@ -3453,7 +3453,7 @@
         <v>92.09999999999999</v>
       </c>
       <c r="H13" s="1">
-        <v>92.09999999999999</v>
+        <v>94.7</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -3470,7 +3470,7 @@
         <v>19</v>
       </c>
       <c r="E14">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F14" s="1">
         <v>60</v>
@@ -3479,7 +3479,7 @@
         <v>63.3</v>
       </c>
       <c r="H14" s="1">
-        <v>63.3</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -3522,7 +3522,7 @@
         <v>19</v>
       </c>
       <c r="E16">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F16" s="1">
         <v>87.5</v>
@@ -3531,7 +3531,7 @@
         <v>79.2</v>
       </c>
       <c r="H16" s="1">
-        <v>79.2</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -3539,25 +3539,25 @@
         <v>32</v>
       </c>
       <c r="B17">
+        <v>33</v>
+      </c>
+      <c r="C17">
         <v>31</v>
       </c>
-      <c r="C17">
-        <v>29</v>
-      </c>
       <c r="D17">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E17">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F17" s="1">
-        <v>93.5</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="G17" s="1">
-        <v>96.8</v>
+        <v>97</v>
       </c>
       <c r="H17" s="1">
-        <v>96.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -3574,7 +3574,7 @@
         <v>16</v>
       </c>
       <c r="E18">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F18" s="1">
         <v>57.1</v>
@@ -3583,7 +3583,7 @@
         <v>57.1</v>
       </c>
       <c r="H18" s="1">
-        <v>57.1</v>
+        <v>78.59999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -3600,7 +3600,7 @@
         <v>30</v>
       </c>
       <c r="E19">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F19" s="1">
         <v>81.09999999999999</v>
@@ -3609,7 +3609,7 @@
         <v>81.09999999999999</v>
       </c>
       <c r="H19" s="1">
-        <v>81.09999999999999</v>
+        <v>94.59999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -3756,7 +3756,7 @@
         <v>9</v>
       </c>
       <c r="E25">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F25" s="1">
         <v>21.7</v>
@@ -3765,7 +3765,7 @@
         <v>39.1</v>
       </c>
       <c r="H25" s="1">
-        <v>39.1</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -3782,7 +3782,7 @@
         <v>15</v>
       </c>
       <c r="E26">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F26" s="1">
         <v>29</v>
@@ -3791,7 +3791,7 @@
         <v>48.4</v>
       </c>
       <c r="H26" s="1">
-        <v>48.4</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -3808,7 +3808,7 @@
         <v>13</v>
       </c>
       <c r="E27">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F27" s="1">
         <v>47.6</v>
@@ -3817,7 +3817,7 @@
         <v>61.9</v>
       </c>
       <c r="H27" s="1">
-        <v>61.9</v>
+        <v>76.2</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -3834,7 +3834,7 @@
         <v>23</v>
       </c>
       <c r="E28">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F28" s="1">
         <v>84</v>
@@ -3843,7 +3843,7 @@
         <v>92</v>
       </c>
       <c r="H28" s="1">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -3860,7 +3860,7 @@
         <v>24</v>
       </c>
       <c r="E29">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F29" s="1">
         <v>70</v>
@@ -3869,7 +3869,7 @@
         <v>80</v>
       </c>
       <c r="H29" s="1">
-        <v>80</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -3886,7 +3886,7 @@
         <v>11</v>
       </c>
       <c r="E30">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F30" s="1">
         <v>42.3</v>
@@ -3895,7 +3895,7 @@
         <v>42.3</v>
       </c>
       <c r="H30" s="1">
-        <v>42.3</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -3912,7 +3912,7 @@
         <v>21</v>
       </c>
       <c r="E31">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F31" s="1">
         <v>59.4</v>
@@ -3921,7 +3921,7 @@
         <v>65.59999999999999</v>
       </c>
       <c r="H31" s="1">
-        <v>65.59999999999999</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -3938,7 +3938,7 @@
         <v>11</v>
       </c>
       <c r="E32">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F32" s="1">
         <v>80</v>
@@ -3947,7 +3947,7 @@
         <v>73.3</v>
       </c>
       <c r="H32" s="1">
-        <v>73.3</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -3964,7 +3964,7 @@
         <v>17</v>
       </c>
       <c r="E33">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F33" s="1">
         <v>76.90000000000001</v>
@@ -3973,7 +3973,7 @@
         <v>65.40000000000001</v>
       </c>
       <c r="H33" s="1">
-        <v>65.40000000000001</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -3981,25 +3981,25 @@
         <v>49</v>
       </c>
       <c r="B34">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D34">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E34">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F34" s="1">
-        <v>57.1</v>
+        <v>60</v>
       </c>
       <c r="G34" s="1">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="H34" s="1">
-        <v>64.3</v>
+        <v>73.3</v>
       </c>
     </row>
   </sheetData>

--- a/Totales Generales20232.xlsx
+++ b/Totales Generales20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="59">
   <si>
     <t>Semestre</t>
   </si>
@@ -27,6 +27,15 @@
   </si>
   <si>
     <t>Tot</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>8</t>
   </si>
   <si>
     <t>7</t>
@@ -547,13 +556,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="13" max="13" width="9.140625" style="1"/>
+    <col min="16" max="16" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:16">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -593,95 +602,122 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C2">
         <v>192</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>6</v>
+      </c>
+      <c r="F2">
+        <v>4</v>
+      </c>
+      <c r="G2">
         <v>3</v>
       </c>
-      <c r="E2">
+      <c r="H2">
         <v>10</v>
       </c>
-      <c r="F2">
+      <c r="I2">
         <v>8</v>
       </c>
-      <c r="G2">
+      <c r="J2">
         <v>13</v>
       </c>
-      <c r="H2">
+      <c r="K2">
         <v>6</v>
       </c>
-      <c r="I2">
+      <c r="L2">
         <v>24</v>
       </c>
-      <c r="J2">
+      <c r="M2">
         <v>25</v>
       </c>
-      <c r="K2">
+      <c r="N2">
         <v>93</v>
       </c>
-      <c r="L2">
+      <c r="O2">
         <v>99</v>
       </c>
-      <c r="M2" s="1">
+      <c r="P2" s="1">
         <v>51.6</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C3">
         <v>220</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
         <v>3</v>
       </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
         <v>6</v>
       </c>
-      <c r="H3">
+      <c r="K3">
         <v>6</v>
       </c>
-      <c r="I3">
+      <c r="L3">
         <v>16</v>
       </c>
-      <c r="J3">
+      <c r="M3">
         <v>40</v>
       </c>
-      <c r="K3">
+      <c r="N3">
         <v>147</v>
       </c>
-      <c r="L3">
+      <c r="O3">
         <v>73</v>
       </c>
-      <c r="M3" s="1">
+      <c r="P3" s="1">
         <v>33.2</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C4">
         <v>189</v>
@@ -690,80 +726,98 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
         <v>4</v>
       </c>
-      <c r="H4">
+      <c r="K4">
         <v>8</v>
       </c>
-      <c r="I4">
+      <c r="L4">
         <v>9</v>
       </c>
-      <c r="J4">
+      <c r="M4">
         <v>17</v>
       </c>
-      <c r="K4">
+      <c r="N4">
         <v>148</v>
       </c>
-      <c r="L4">
+      <c r="O4">
         <v>41</v>
       </c>
-      <c r="M4" s="1">
+      <c r="P4" s="1">
         <v>21.7</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C5">
         <v>601</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>6</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
         <v>5</v>
       </c>
-      <c r="E5">
+      <c r="H5">
         <v>15</v>
       </c>
-      <c r="F5">
+      <c r="I5">
         <v>9</v>
       </c>
-      <c r="G5">
+      <c r="J5">
         <v>23</v>
       </c>
-      <c r="H5">
+      <c r="K5">
         <v>20</v>
       </c>
-      <c r="I5">
+      <c r="L5">
         <v>49</v>
       </c>
-      <c r="J5">
+      <c r="M5">
         <v>82</v>
       </c>
-      <c r="K5">
+      <c r="N5">
         <v>388</v>
       </c>
-      <c r="L5">
+      <c r="O5">
         <v>213</v>
       </c>
-      <c r="M5" s="1">
+      <c r="P5" s="1">
         <v>35.4</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C6">
         <v>128</v>
@@ -772,80 +826,98 @@
         <v>2</v>
       </c>
       <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
         <v>16</v>
       </c>
-      <c r="F6">
+      <c r="I6">
         <v>12</v>
       </c>
-      <c r="G6">
+      <c r="J6">
         <v>10</v>
       </c>
-      <c r="H6">
+      <c r="K6">
         <v>20</v>
       </c>
-      <c r="I6">
+      <c r="L6">
         <v>16</v>
       </c>
-      <c r="J6">
+      <c r="M6">
         <v>14</v>
       </c>
-      <c r="K6">
+      <c r="N6">
         <v>29</v>
       </c>
-      <c r="L6">
+      <c r="O6">
         <v>99</v>
       </c>
-      <c r="M6" s="1">
+      <c r="P6" s="1">
         <v>77.3</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C7">
         <v>130</v>
       </c>
       <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
         <v>3</v>
       </c>
-      <c r="E7">
+      <c r="H7">
         <v>3</v>
       </c>
-      <c r="F7">
+      <c r="I7">
         <v>3</v>
       </c>
-      <c r="G7">
+      <c r="J7">
         <v>8</v>
       </c>
-      <c r="H7">
+      <c r="K7">
         <v>12</v>
       </c>
-      <c r="I7">
+      <c r="L7">
         <v>9</v>
       </c>
-      <c r="J7">
+      <c r="M7">
         <v>26</v>
       </c>
-      <c r="K7">
+      <c r="N7">
         <v>66</v>
       </c>
-      <c r="L7">
+      <c r="O7">
         <v>64</v>
       </c>
-      <c r="M7" s="1">
+      <c r="P7" s="1">
         <v>49.2</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C8">
         <v>114</v>
@@ -854,109 +926,136 @@
         <v>0</v>
       </c>
       <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
         <v>3</v>
       </c>
-      <c r="F8">
+      <c r="I8">
         <v>6</v>
       </c>
-      <c r="G8">
+      <c r="J8">
         <v>3</v>
       </c>
-      <c r="H8">
+      <c r="K8">
         <v>4</v>
       </c>
-      <c r="I8">
+      <c r="L8">
         <v>8</v>
       </c>
-      <c r="J8">
+      <c r="M8">
         <v>19</v>
       </c>
-      <c r="K8">
+      <c r="N8">
         <v>71</v>
       </c>
-      <c r="L8">
+      <c r="O8">
         <v>43</v>
       </c>
-      <c r="M8" s="1">
+      <c r="P8" s="1">
         <v>37.7</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:16">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C9">
         <v>372</v>
       </c>
       <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9">
+        <v>6</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
         <v>5</v>
       </c>
-      <c r="E9">
+      <c r="H9">
         <v>22</v>
       </c>
-      <c r="F9">
+      <c r="I9">
         <v>21</v>
       </c>
-      <c r="G9">
+      <c r="J9">
         <v>21</v>
       </c>
-      <c r="H9">
+      <c r="K9">
         <v>36</v>
       </c>
-      <c r="I9">
+      <c r="L9">
         <v>33</v>
       </c>
-      <c r="J9">
+      <c r="M9">
         <v>59</v>
       </c>
-      <c r="K9">
+      <c r="N9">
         <v>166</v>
       </c>
-      <c r="L9">
+      <c r="O9">
         <v>206</v>
       </c>
-      <c r="M9" s="1">
+      <c r="P9" s="1">
         <v>55.4</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:16">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C10">
         <v>973</v>
       </c>
       <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10">
+        <v>12</v>
+      </c>
+      <c r="F10">
+        <v>5</v>
+      </c>
+      <c r="G10">
         <v>10</v>
       </c>
-      <c r="E10">
+      <c r="H10">
         <v>37</v>
       </c>
-      <c r="F10">
+      <c r="I10">
         <v>30</v>
       </c>
-      <c r="G10">
+      <c r="J10">
         <v>44</v>
       </c>
-      <c r="H10">
+      <c r="K10">
         <v>56</v>
       </c>
-      <c r="I10">
+      <c r="L10">
         <v>82</v>
       </c>
-      <c r="J10">
+      <c r="M10">
         <v>141</v>
       </c>
-      <c r="K10">
+      <c r="N10">
         <v>554</v>
       </c>
-      <c r="L10">
+      <c r="O10">
         <v>419</v>
       </c>
-      <c r="M10" s="1">
+      <c r="P10" s="1">
         <v>43.1</v>
       </c>
     </row>
@@ -967,13 +1066,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="13" max="13" width="9.140625" style="1"/>
+    <col min="16" max="16" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:16">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1013,95 +1112,122 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C2">
         <v>192</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>10</v>
+      </c>
+      <c r="G2">
         <v>4</v>
       </c>
-      <c r="E2">
+      <c r="H2">
         <v>10</v>
       </c>
-      <c r="F2">
+      <c r="I2">
         <v>3</v>
       </c>
-      <c r="G2">
+      <c r="J2">
         <v>10</v>
       </c>
-      <c r="H2">
+      <c r="K2">
         <v>9</v>
       </c>
-      <c r="I2">
+      <c r="L2">
         <v>16</v>
       </c>
-      <c r="J2">
+      <c r="M2">
         <v>21</v>
       </c>
-      <c r="K2">
+      <c r="N2">
         <v>108</v>
       </c>
-      <c r="L2">
+      <c r="O2">
         <v>84</v>
       </c>
-      <c r="M2" s="1">
+      <c r="P2" s="1">
         <v>43.8</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C3">
         <v>220</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
         <v>3</v>
       </c>
-      <c r="F3">
+      <c r="I3">
         <v>3</v>
       </c>
-      <c r="G3">
+      <c r="J3">
         <v>4</v>
       </c>
-      <c r="H3">
+      <c r="K3">
         <v>7</v>
       </c>
-      <c r="I3">
+      <c r="L3">
         <v>18</v>
       </c>
-      <c r="J3">
+      <c r="M3">
         <v>23</v>
       </c>
-      <c r="K3">
+      <c r="N3">
         <v>160</v>
       </c>
-      <c r="L3">
+      <c r="O3">
         <v>60</v>
       </c>
-      <c r="M3" s="1">
+      <c r="P3" s="1">
         <v>27.3</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C4">
         <v>189</v>
@@ -1110,162 +1236,198 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
         <v>4</v>
       </c>
-      <c r="H4">
+      <c r="K4">
         <v>6</v>
       </c>
-      <c r="I4">
+      <c r="L4">
         <v>11</v>
       </c>
-      <c r="J4">
+      <c r="M4">
         <v>12</v>
       </c>
-      <c r="K4">
+      <c r="N4">
         <v>153</v>
       </c>
-      <c r="L4">
+      <c r="O4">
         <v>36</v>
       </c>
-      <c r="M4" s="1">
+      <c r="P4" s="1">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C5">
         <v>601</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>10</v>
+      </c>
+      <c r="G5">
         <v>6</v>
       </c>
-      <c r="E5">
+      <c r="H5">
         <v>15</v>
       </c>
-      <c r="F5">
+      <c r="I5">
         <v>7</v>
       </c>
-      <c r="G5">
+      <c r="J5">
         <v>18</v>
       </c>
-      <c r="H5">
+      <c r="K5">
         <v>22</v>
       </c>
-      <c r="I5">
+      <c r="L5">
         <v>45</v>
       </c>
-      <c r="J5">
+      <c r="M5">
         <v>56</v>
       </c>
-      <c r="K5">
+      <c r="N5">
         <v>421</v>
       </c>
-      <c r="L5">
+      <c r="O5">
         <v>180</v>
       </c>
-      <c r="M5" s="1">
+      <c r="P5" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C6">
         <v>128</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G6">
         <v>8</v>
       </c>
       <c r="H6">
+        <v>9</v>
+      </c>
+      <c r="I6">
+        <v>9</v>
+      </c>
+      <c r="J6">
+        <v>8</v>
+      </c>
+      <c r="K6">
         <v>19</v>
       </c>
-      <c r="I6">
+      <c r="L6">
         <v>12</v>
       </c>
-      <c r="J6">
+      <c r="M6">
         <v>13</v>
       </c>
-      <c r="K6">
+      <c r="N6">
         <v>42</v>
       </c>
-      <c r="L6">
+      <c r="O6">
         <v>86</v>
       </c>
-      <c r="M6" s="1">
+      <c r="P6" s="1">
         <v>67.2</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C7">
         <v>130</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7">
         <v>7</v>
       </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-      <c r="H7">
+      <c r="J7">
+        <v>2</v>
+      </c>
+      <c r="K7">
         <v>7</v>
       </c>
-      <c r="I7">
+      <c r="L7">
         <v>10</v>
       </c>
-      <c r="J7">
+      <c r="M7">
         <v>16</v>
       </c>
-      <c r="K7">
+      <c r="N7">
         <v>84</v>
       </c>
-      <c r="L7">
+      <c r="O7">
         <v>46</v>
       </c>
-      <c r="M7" s="1">
+      <c r="P7" s="1">
         <v>35.4</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C8">
         <v>114</v>
@@ -1274,109 +1436,136 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>2</v>
+      </c>
+      <c r="I8">
         <v>4</v>
       </c>
-      <c r="G8">
+      <c r="J8">
         <v>7</v>
       </c>
-      <c r="H8">
+      <c r="K8">
         <v>8</v>
       </c>
-      <c r="I8">
+      <c r="L8">
         <v>10</v>
       </c>
-      <c r="J8">
+      <c r="M8">
         <v>13</v>
       </c>
-      <c r="K8">
+      <c r="N8">
         <v>70</v>
       </c>
-      <c r="L8">
+      <c r="O8">
         <v>44</v>
       </c>
-      <c r="M8" s="1">
+      <c r="P8" s="1">
         <v>38.6</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:16">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C9">
         <v>372</v>
       </c>
       <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>5</v>
+      </c>
+      <c r="F9">
+        <v>3</v>
+      </c>
+      <c r="G9">
         <v>10</v>
       </c>
-      <c r="E9">
+      <c r="H9">
         <v>13</v>
       </c>
-      <c r="F9">
+      <c r="I9">
         <v>20</v>
       </c>
-      <c r="G9">
+      <c r="J9">
         <v>17</v>
       </c>
-      <c r="H9">
+      <c r="K9">
         <v>34</v>
       </c>
-      <c r="I9">
+      <c r="L9">
         <v>32</v>
       </c>
-      <c r="J9">
+      <c r="M9">
         <v>42</v>
       </c>
-      <c r="K9">
+      <c r="N9">
         <v>196</v>
       </c>
-      <c r="L9">
+      <c r="O9">
         <v>176</v>
       </c>
-      <c r="M9" s="1">
+      <c r="P9" s="1">
         <v>47.3</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:16">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C10">
         <v>973</v>
       </c>
       <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>6</v>
+      </c>
+      <c r="F10">
+        <v>13</v>
+      </c>
+      <c r="G10">
         <v>16</v>
       </c>
-      <c r="E10">
+      <c r="H10">
         <v>28</v>
       </c>
-      <c r="F10">
+      <c r="I10">
         <v>27</v>
       </c>
-      <c r="G10">
+      <c r="J10">
         <v>35</v>
       </c>
-      <c r="H10">
+      <c r="K10">
         <v>56</v>
       </c>
-      <c r="I10">
+      <c r="L10">
         <v>77</v>
       </c>
-      <c r="J10">
+      <c r="M10">
         <v>98</v>
       </c>
-      <c r="K10">
+      <c r="N10">
         <v>617</v>
       </c>
-      <c r="L10">
+      <c r="O10">
         <v>356</v>
       </c>
-      <c r="M10" s="1">
+      <c r="P10" s="1">
         <v>36.6</v>
       </c>
     </row>
@@ -1387,13 +1576,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="13" max="13" width="9.140625" style="1"/>
+    <col min="16" max="16" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:16">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1433,13 +1622,22 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C2">
         <v>192</v>
@@ -1448,80 +1646,98 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
         <v>4</v>
       </c>
-      <c r="H2">
-        <v>8</v>
-      </c>
-      <c r="I2">
-        <v>21</v>
-      </c>
       <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>4</v>
+      </c>
+      <c r="L2">
+        <v>9</v>
+      </c>
+      <c r="M2">
+        <v>20</v>
+      </c>
+      <c r="N2">
         <v>143</v>
       </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>192</v>
-      </c>
-      <c r="M2" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="O2">
+        <v>49</v>
+      </c>
+      <c r="P2" s="1">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C3">
         <v>220</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
         <v>3</v>
       </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
       <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
         <v>5</v>
       </c>
-      <c r="I3">
+      <c r="L3">
         <v>12</v>
       </c>
-      <c r="J3">
+      <c r="M3">
         <v>37</v>
       </c>
-      <c r="K3">
+      <c r="N3">
         <v>159</v>
       </c>
-      <c r="L3">
+      <c r="O3">
         <v>61</v>
       </c>
-      <c r="M3" s="1">
+      <c r="P3" s="1">
         <v>27.7</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C4">
         <v>189</v>
@@ -1530,7 +1746,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -1539,153 +1755,189 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
         <v>6</v>
       </c>
-      <c r="J4">
+      <c r="M4">
         <v>4</v>
       </c>
-      <c r="K4">
+      <c r="N4">
         <v>176</v>
       </c>
-      <c r="L4">
+      <c r="O4">
         <v>13</v>
       </c>
-      <c r="M4" s="1">
+      <c r="P4" s="1">
         <v>6.9</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C5">
         <v>601</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
         <v>3</v>
       </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
       <c r="G5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H5">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="I5">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>184</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>335</v>
+        <v>10</v>
       </c>
       <c r="L5">
-        <v>266</v>
-      </c>
-      <c r="M5" s="1">
-        <v>44.3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+        <v>27</v>
+      </c>
+      <c r="M5">
+        <v>61</v>
+      </c>
+      <c r="N5">
+        <v>478</v>
+      </c>
+      <c r="O5">
+        <v>123</v>
+      </c>
+      <c r="P5" s="1">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C6">
         <v>128</v>
       </c>
       <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
         <v>3</v>
       </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
       <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
         <v>3</v>
       </c>
-      <c r="G6">
-        <v>10</v>
-      </c>
-      <c r="H6">
-        <v>13</v>
-      </c>
-      <c r="I6">
-        <v>22</v>
-      </c>
-      <c r="J6">
+      <c r="K6">
+        <v>14</v>
+      </c>
+      <c r="L6">
+        <v>11</v>
+      </c>
+      <c r="M6">
+        <v>24</v>
+      </c>
+      <c r="N6">
+        <v>62</v>
+      </c>
+      <c r="O6">
         <v>66</v>
       </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>127</v>
-      </c>
-      <c r="M6" s="1">
-        <v>99.2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="P6" s="1">
+        <v>51.6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C7">
         <v>130</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
         <v>3</v>
       </c>
-      <c r="F7">
-        <v>2</v>
-      </c>
-      <c r="G7">
+      <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7">
         <v>5</v>
       </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
         <v>7</v>
       </c>
-      <c r="J7">
+      <c r="M7">
         <v>15</v>
       </c>
-      <c r="K7">
+      <c r="N7">
         <v>95</v>
       </c>
-      <c r="L7">
+      <c r="O7">
         <v>35</v>
       </c>
-      <c r="M7" s="1">
+      <c r="P7" s="1">
         <v>26.9</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C8">
         <v>114</v>
@@ -1694,7 +1946,7 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1706,98 +1958,125 @@
         <v>2</v>
       </c>
       <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>2</v>
+      </c>
+      <c r="L8">
         <v>4</v>
       </c>
-      <c r="J8">
+      <c r="M8">
         <v>13</v>
       </c>
-      <c r="K8">
+      <c r="N8">
         <v>93</v>
       </c>
-      <c r="L8">
+      <c r="O8">
         <v>21</v>
       </c>
-      <c r="M8" s="1">
+      <c r="P8" s="1">
         <v>18.4</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:16">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C9">
         <v>372</v>
       </c>
       <c r="D9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F9">
         <v>5</v>
       </c>
       <c r="G9">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H9">
+        <v>5</v>
+      </c>
+      <c r="I9">
+        <v>3</v>
+      </c>
+      <c r="J9">
+        <v>8</v>
+      </c>
+      <c r="K9">
+        <v>17</v>
+      </c>
+      <c r="L9">
+        <v>22</v>
+      </c>
+      <c r="M9">
+        <v>52</v>
+      </c>
+      <c r="N9">
+        <v>250</v>
+      </c>
+      <c r="O9">
+        <v>122</v>
+      </c>
+      <c r="P9" s="1">
+        <v>32.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" t="s">
         <v>16</v>
-      </c>
-      <c r="I9">
-        <v>33</v>
-      </c>
-      <c r="J9">
-        <v>94</v>
-      </c>
-      <c r="K9">
-        <v>189</v>
-      </c>
-      <c r="L9">
-        <v>183</v>
-      </c>
-      <c r="M9" s="1">
-        <v>49.2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" t="s">
-        <v>13</v>
       </c>
       <c r="C10">
         <v>973</v>
       </c>
       <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
         <v>8</v>
       </c>
-      <c r="E10">
+      <c r="F10">
+        <v>8</v>
+      </c>
+      <c r="G10">
+        <v>10</v>
+      </c>
+      <c r="H10">
+        <v>8</v>
+      </c>
+      <c r="I10">
+        <v>9</v>
+      </c>
+      <c r="J10">
         <v>12</v>
       </c>
-      <c r="F10">
-        <v>10</v>
-      </c>
-      <c r="G10">
-        <v>20</v>
-      </c>
-      <c r="H10">
-        <v>30</v>
-      </c>
-      <c r="I10">
-        <v>72</v>
-      </c>
-      <c r="J10">
-        <v>278</v>
-      </c>
       <c r="K10">
-        <v>524</v>
+        <v>27</v>
       </c>
       <c r="L10">
-        <v>449</v>
-      </c>
-      <c r="M10" s="1">
-        <v>46.1</v>
+        <v>49</v>
+      </c>
+      <c r="M10">
+        <v>113</v>
+      </c>
+      <c r="N10">
+        <v>728</v>
+      </c>
+      <c r="O10">
+        <v>245</v>
+      </c>
+      <c r="P10" s="1">
+        <v>25.2</v>
       </c>
     </row>
   </sheetData>
@@ -1807,15 +2086,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="12" max="12" width="9.140625" style="1"/>
+    <col min="15" max="15" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>2</v>
@@ -1850,10 +2129,19 @@
       <c r="L1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B2">
         <v>25</v>
@@ -1865,33 +2153,42 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
         <v>5</v>
       </c>
-      <c r="I2">
+      <c r="M2">
         <v>13</v>
       </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>25</v>
-      </c>
-      <c r="L2" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="N2">
+        <v>12</v>
+      </c>
+      <c r="O2" s="1">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B3">
         <v>39</v>
@@ -1900,36 +2197,45 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
         <v>4</v>
       </c>
-      <c r="I3">
+      <c r="M3">
         <v>30</v>
       </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>39</v>
-      </c>
-      <c r="L3" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="N3">
+        <v>9</v>
+      </c>
+      <c r="O3" s="1">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>31</v>
@@ -1938,36 +2244,45 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
         <v>3</v>
       </c>
-      <c r="I4">
+      <c r="M4">
         <v>24</v>
       </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>31</v>
-      </c>
-      <c r="L4" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="N4">
+        <v>7</v>
+      </c>
+      <c r="O4" s="1">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B5">
         <v>35</v>
@@ -1976,36 +2291,45 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
         <v>29</v>
       </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>35</v>
-      </c>
-      <c r="L5" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="N5">
+        <v>6</v>
+      </c>
+      <c r="O5" s="1">
+        <v>17.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B6">
         <v>24</v>
@@ -2026,24 +2350,33 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="M6">
         <v>17</v>
       </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>24</v>
-      </c>
-      <c r="L6" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="N6">
+        <v>7</v>
+      </c>
+      <c r="O6" s="1">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B7">
         <v>38</v>
@@ -2061,27 +2394,36 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>2</v>
+      </c>
+      <c r="L7">
         <v>4</v>
       </c>
-      <c r="I7">
+      <c r="M7">
         <v>30</v>
       </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>38</v>
-      </c>
-      <c r="L7" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+      <c r="N7">
+        <v>8</v>
+      </c>
+      <c r="O7" s="1">
+        <v>21.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B8">
         <v>29</v>
@@ -2099,33 +2441,42 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>2</v>
+      </c>
+      <c r="K8">
         <v>4</v>
       </c>
-      <c r="I8">
+      <c r="L8">
         <v>22</v>
       </c>
-      <c r="J8">
-        <v>1</v>
-      </c>
-      <c r="K8">
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
         <v>28</v>
       </c>
-      <c r="L8" s="1">
+      <c r="O8" s="1">
         <v>96.59999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:15">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B9">
         <v>42</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -2134,7 +2485,7 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2143,21 +2494,30 @@
         <v>0</v>
       </c>
       <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
         <v>3</v>
       </c>
-      <c r="J9">
+      <c r="M9">
         <v>38</v>
       </c>
-      <c r="K9">
+      <c r="N9">
         <v>4</v>
       </c>
-      <c r="L9" s="1">
+      <c r="O9" s="1">
         <v>9.5</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:15">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B10">
         <v>35</v>
@@ -2166,36 +2526,45 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
         <v>4</v>
       </c>
-      <c r="J10">
+      <c r="M10">
         <v>29</v>
       </c>
-      <c r="K10">
+      <c r="N10">
         <v>6</v>
       </c>
-      <c r="L10" s="1">
+      <c r="O10" s="1">
         <v>17.1</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:15">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B11">
         <v>45</v>
@@ -2210,30 +2579,39 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
         <v>3</v>
       </c>
-      <c r="H11">
+      <c r="K11">
         <v>6</v>
       </c>
-      <c r="I11">
+      <c r="L11">
         <v>4</v>
       </c>
-      <c r="J11">
+      <c r="M11">
         <v>31</v>
       </c>
-      <c r="K11">
+      <c r="N11">
         <v>14</v>
       </c>
-      <c r="L11" s="1">
+      <c r="O11" s="1">
         <v>31.1</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:15">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B12">
         <v>31</v>
@@ -2245,7 +2623,7 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -2254,30 +2632,39 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>2</v>
+      </c>
+      <c r="L12">
         <v>4</v>
       </c>
-      <c r="J12">
+      <c r="M12">
         <v>24</v>
       </c>
-      <c r="K12">
+      <c r="N12">
         <v>7</v>
       </c>
-      <c r="L12" s="1">
+      <c r="O12" s="1">
         <v>22.6</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:15">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B13">
         <v>38</v>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -2286,7 +2673,7 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2298,18 +2685,27 @@
         <v>0</v>
       </c>
       <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
         <v>36</v>
       </c>
-      <c r="K13">
-        <v>2</v>
-      </c>
-      <c r="L13" s="1">
+      <c r="N13">
+        <v>2</v>
+      </c>
+      <c r="O13" s="1">
         <v>5.3</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:15">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B14">
         <v>30</v>
@@ -2327,27 +2723,36 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>2</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
         <v>26</v>
       </c>
-      <c r="K14">
+      <c r="N14">
         <v>4</v>
       </c>
-      <c r="L14" s="1">
+      <c r="O14" s="1">
         <v>13.3</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:15">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B15">
         <v>37</v>
@@ -2374,18 +2779,27 @@
         <v>0</v>
       </c>
       <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
         <v>37</v>
       </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B16">
         <v>24</v>
@@ -2394,7 +2808,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -2403,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -2412,18 +2826,27 @@
         <v>0</v>
       </c>
       <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
         <v>23</v>
       </c>
-      <c r="K16">
-        <v>1</v>
-      </c>
-      <c r="L16" s="1">
+      <c r="N16">
+        <v>1</v>
+      </c>
+      <c r="O16" s="1">
         <v>4.2</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:15">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B17">
         <v>33</v>
@@ -2450,18 +2873,27 @@
         <v>0</v>
       </c>
       <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
         <v>33</v>
       </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="L17" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12">
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B18">
         <v>28</v>
@@ -2470,7 +2902,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -2479,27 +2911,36 @@
         <v>0</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
         <v>4</v>
       </c>
-      <c r="I18">
-        <v>1</v>
-      </c>
-      <c r="J18">
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="M18">
         <v>22</v>
       </c>
-      <c r="K18">
+      <c r="N18">
         <v>6</v>
       </c>
-      <c r="L18" s="1">
+      <c r="O18" s="1">
         <v>21.4</v>
       </c>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:15">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B19">
         <v>37</v>
@@ -2523,59 +2964,77 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>2</v>
+      </c>
+      <c r="M19">
         <v>35</v>
       </c>
-      <c r="K19">
-        <v>2</v>
-      </c>
-      <c r="L19" s="1">
+      <c r="N19">
+        <v>2</v>
+      </c>
+      <c r="O19" s="1">
         <v>5.4</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:15">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B20">
         <v>30</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G20">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I20">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20">
-        <v>30</v>
-      </c>
-      <c r="L20" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
+        <v>3</v>
+      </c>
+      <c r="L20">
+        <v>8</v>
+      </c>
+      <c r="M20">
+        <v>12</v>
+      </c>
+      <c r="N20">
+        <v>18</v>
+      </c>
+      <c r="O20" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B21">
         <v>29</v>
@@ -2587,39 +3046,48 @@
         <v>0</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21">
+        <v>2</v>
+      </c>
+      <c r="J21">
+        <v>4</v>
+      </c>
+      <c r="K21">
+        <v>5</v>
+      </c>
+      <c r="L21">
         <v>9</v>
       </c>
-      <c r="I21">
-        <v>10</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>29</v>
-      </c>
-      <c r="L21" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
+      <c r="M21">
+        <v>8</v>
+      </c>
+      <c r="N21">
+        <v>21</v>
+      </c>
+      <c r="O21" s="1">
+        <v>72.40000000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B22">
         <v>23</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -2628,68 +3096,86 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>6</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="M22">
         <v>14</v>
       </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>23</v>
-      </c>
-      <c r="L22" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12">
+      <c r="N22">
+        <v>9</v>
+      </c>
+      <c r="O22" s="1">
+        <v>39.1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B23">
         <v>34</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F23">
+        <v>2</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
         <v>3</v>
       </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-      <c r="H23">
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="L23">
         <v>4</v>
       </c>
-      <c r="I23">
-        <v>21</v>
-      </c>
-      <c r="J23">
-        <v>1</v>
-      </c>
-      <c r="K23">
-        <v>33</v>
-      </c>
-      <c r="L23" s="1">
-        <v>97.09999999999999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12">
+      <c r="M23">
+        <v>22</v>
+      </c>
+      <c r="N23">
+        <v>12</v>
+      </c>
+      <c r="O23" s="1">
+        <v>35.3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
       <c r="A24" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B24">
         <v>12</v>
@@ -2698,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -2710,24 +3196,33 @@
         <v>0</v>
       </c>
       <c r="H24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24">
-        <v>12</v>
-      </c>
-      <c r="L24" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
+        <v>1</v>
+      </c>
+      <c r="L24">
+        <v>2</v>
+      </c>
+      <c r="M24">
+        <v>6</v>
+      </c>
+      <c r="N24">
+        <v>6</v>
+      </c>
+      <c r="O24" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
       <c r="A25" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B25">
         <v>23</v>
@@ -2736,7 +3231,7 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2745,103 +3240,130 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>2</v>
+      </c>
+      <c r="L25">
         <v>8</v>
       </c>
-      <c r="J25">
+      <c r="M25">
         <v>12</v>
       </c>
-      <c r="K25">
+      <c r="N25">
         <v>11</v>
       </c>
-      <c r="L25" s="1">
+      <c r="O25" s="1">
         <v>47.8</v>
       </c>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="1:15">
       <c r="A26" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B26">
         <v>31</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26">
         <v>4</v>
       </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-      <c r="H26">
+      <c r="J26">
+        <v>1</v>
+      </c>
+      <c r="K26">
         <v>3</v>
       </c>
-      <c r="I26">
-        <v>2</v>
-      </c>
-      <c r="J26">
+      <c r="L26">
+        <v>2</v>
+      </c>
+      <c r="M26">
         <v>18</v>
       </c>
-      <c r="K26">
+      <c r="N26">
         <v>13</v>
       </c>
-      <c r="L26" s="1">
+      <c r="O26" s="1">
         <v>41.9</v>
       </c>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:15">
       <c r="A27" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B27">
         <v>21</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27">
         <v>0</v>
       </c>
       <c r="H27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>2</v>
+      </c>
+      <c r="L27">
+        <v>1</v>
+      </c>
+      <c r="M27">
         <v>16</v>
       </c>
-      <c r="K27">
+      <c r="N27">
         <v>5</v>
       </c>
-      <c r="L27" s="1">
+      <c r="O27" s="1">
         <v>23.8</v>
       </c>
     </row>
-    <row r="28" spans="1:12">
+    <row r="28" spans="1:15">
       <c r="A28" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B28">
         <v>25</v>
@@ -2850,7 +3372,7 @@
         <v>0</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2859,7 +3381,7 @@
         <v>0</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -2868,18 +3390,27 @@
         <v>0</v>
       </c>
       <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
         <v>24</v>
       </c>
-      <c r="K28">
-        <v>1</v>
-      </c>
-      <c r="L28" s="1">
+      <c r="N28">
+        <v>1</v>
+      </c>
+      <c r="O28" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:12">
+    <row r="29" spans="1:15">
       <c r="A29" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B29">
         <v>30</v>
@@ -2894,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -2903,21 +3434,30 @@
         <v>0</v>
       </c>
       <c r="I29">
+        <v>1</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
         <v>4</v>
       </c>
-      <c r="J29">
+      <c r="M29">
         <v>25</v>
       </c>
-      <c r="K29">
+      <c r="N29">
         <v>5</v>
       </c>
-      <c r="L29" s="1">
+      <c r="O29" s="1">
         <v>16.7</v>
       </c>
     </row>
-    <row r="30" spans="1:12">
+    <row r="30" spans="1:15">
       <c r="A30" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B30">
         <v>26</v>
@@ -2941,21 +3481,30 @@
         <v>0</v>
       </c>
       <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
         <v>4</v>
       </c>
-      <c r="J30">
+      <c r="M30">
         <v>22</v>
       </c>
-      <c r="K30">
+      <c r="N30">
         <v>4</v>
       </c>
-      <c r="L30" s="1">
+      <c r="O30" s="1">
         <v>15.4</v>
       </c>
     </row>
-    <row r="31" spans="1:12">
+    <row r="31" spans="1:15">
       <c r="A31" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B31">
         <v>32</v>
@@ -2973,27 +3522,36 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>1</v>
+      </c>
+      <c r="K31">
+        <v>1</v>
+      </c>
+      <c r="L31">
         <v>6</v>
       </c>
-      <c r="J31">
+      <c r="M31">
         <v>24</v>
       </c>
-      <c r="K31">
+      <c r="N31">
         <v>8</v>
       </c>
-      <c r="L31" s="1">
+      <c r="O31" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:12">
+    <row r="32" spans="1:15">
       <c r="A32" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B32">
         <v>15</v>
@@ -3002,7 +3560,7 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -3011,27 +3569,36 @@
         <v>0</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32">
         <v>0</v>
       </c>
       <c r="I32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>1</v>
+      </c>
+      <c r="M32">
         <v>13</v>
       </c>
-      <c r="K32">
-        <v>2</v>
-      </c>
-      <c r="L32" s="1">
+      <c r="N32">
+        <v>2</v>
+      </c>
+      <c r="O32" s="1">
         <v>13.3</v>
       </c>
     </row>
-    <row r="33" spans="1:12">
+    <row r="33" spans="1:15">
       <c r="A33" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B33">
         <v>26</v>
@@ -3052,24 +3619,33 @@
         <v>0</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>1</v>
+      </c>
+      <c r="L33">
+        <v>2</v>
+      </c>
+      <c r="M33">
         <v>23</v>
       </c>
-      <c r="K33">
+      <c r="N33">
         <v>3</v>
       </c>
-      <c r="L33" s="1">
+      <c r="O33" s="1">
         <v>11.5</v>
       </c>
     </row>
-    <row r="34" spans="1:12">
+    <row r="34" spans="1:15">
       <c r="A34" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B34">
         <v>15</v>
@@ -3078,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="D34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -3090,18 +3666,27 @@
         <v>1</v>
       </c>
       <c r="H34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
+        <v>1</v>
+      </c>
+      <c r="K34">
+        <v>2</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
         <v>11</v>
       </c>
-      <c r="K34">
+      <c r="N34">
         <v>4</v>
       </c>
-      <c r="L34" s="1">
+      <c r="O34" s="1">
         <v>26.7</v>
       </c>
     </row>
@@ -3120,33 +3705,33 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B2">
         <v>25</v>
@@ -3158,7 +3743,7 @@
         <v>10</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F2" s="1">
         <v>40</v>
@@ -3167,12 +3752,12 @@
         <v>40</v>
       </c>
       <c r="H2" s="1">
-        <v>0</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B3">
         <v>39</v>
@@ -3184,7 +3769,7 @@
         <v>21</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F3" s="1">
         <v>51.3</v>
@@ -3193,12 +3778,12 @@
         <v>53.8</v>
       </c>
       <c r="H3" s="1">
-        <v>0</v>
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>31</v>
@@ -3210,7 +3795,7 @@
         <v>18</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F4" s="1">
         <v>41.9</v>
@@ -3219,12 +3804,12 @@
         <v>58.1</v>
       </c>
       <c r="H4" s="1">
-        <v>0</v>
+        <v>77.40000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B5">
         <v>35</v>
@@ -3236,7 +3821,7 @@
         <v>21</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F5" s="1">
         <v>54.3</v>
@@ -3245,12 +3830,12 @@
         <v>60</v>
       </c>
       <c r="H5" s="1">
-        <v>0</v>
+        <v>82.90000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B6">
         <v>24</v>
@@ -3262,7 +3847,7 @@
         <v>11</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F6" s="1">
         <v>33.3</v>
@@ -3271,12 +3856,12 @@
         <v>45.8</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>70.8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B7">
         <v>38</v>
@@ -3288,7 +3873,7 @@
         <v>27</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F7" s="1">
         <v>60.5</v>
@@ -3297,12 +3882,12 @@
         <v>71.09999999999999</v>
       </c>
       <c r="H7" s="1">
-        <v>0</v>
+        <v>78.90000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B8">
         <v>29</v>
@@ -3328,7 +3913,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B9">
         <v>42</v>
@@ -3354,7 +3939,7 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B10">
         <v>35</v>
@@ -3380,7 +3965,7 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B11">
         <v>45</v>
@@ -3406,7 +3991,7 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B12">
         <v>31</v>
@@ -3432,7 +4017,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B13">
         <v>38</v>
@@ -3458,7 +4043,7 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B14">
         <v>30</v>
@@ -3484,7 +4069,7 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B15">
         <v>37</v>
@@ -3510,7 +4095,7 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B16">
         <v>24</v>
@@ -3536,7 +4121,7 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B17">
         <v>33</v>
@@ -3562,7 +4147,7 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B18">
         <v>28</v>
@@ -3588,7 +4173,7 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B19">
         <v>37</v>
@@ -3614,7 +4199,7 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B20">
         <v>30</v>
@@ -3626,7 +4211,7 @@
         <v>8</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F20" s="1">
         <v>16.7</v>
@@ -3635,12 +4220,12 @@
         <v>26.7</v>
       </c>
       <c r="H20" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B21">
         <v>29</v>
@@ -3652,7 +4237,7 @@
         <v>4</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F21" s="1">
         <v>10.3</v>
@@ -3661,12 +4246,12 @@
         <v>13.8</v>
       </c>
       <c r="H21" s="1">
-        <v>0</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B22">
         <v>23</v>
@@ -3678,7 +4263,7 @@
         <v>12</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F22" s="1">
         <v>34.8</v>
@@ -3687,12 +4272,12 @@
         <v>52.2</v>
       </c>
       <c r="H22" s="1">
-        <v>0</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B23">
         <v>34</v>
@@ -3704,7 +4289,7 @@
         <v>14</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="F23" s="1">
         <v>26.5</v>
@@ -3713,12 +4298,12 @@
         <v>41.2</v>
       </c>
       <c r="H23" s="1">
-        <v>2.9</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B24">
         <v>12</v>
@@ -3730,7 +4315,7 @@
         <v>4</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F24" s="1">
         <v>33.3</v>
@@ -3739,12 +4324,12 @@
         <v>33.3</v>
       </c>
       <c r="H24" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B25">
         <v>23</v>
@@ -3770,7 +4355,7 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B26">
         <v>31</v>
@@ -3796,7 +4381,7 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B27">
         <v>21</v>
@@ -3822,7 +4407,7 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B28">
         <v>25</v>
@@ -3848,7 +4433,7 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B29">
         <v>30</v>
@@ -3874,7 +4459,7 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B30">
         <v>26</v>
@@ -3900,7 +4485,7 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B31">
         <v>32</v>
@@ -3926,7 +4511,7 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B32">
         <v>15</v>
@@ -3952,7 +4537,7 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B33">
         <v>26</v>
@@ -3978,7 +4563,7 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B34">
         <v>15</v>

--- a/Totales Generales20232.xlsx
+++ b/Totales Generales20232.xlsx
@@ -1708,19 +1708,19 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M3">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N3">
         <v>159</v>
@@ -1808,19 +1808,19 @@
         <v>3</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M5">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="N5">
         <v>478</v>
@@ -1852,34 +1852,34 @@
         <v>5</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6">
         <v>3</v>
       </c>
       <c r="K6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M6">
         <v>24</v>
       </c>
       <c r="N6">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="O6">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="P6" s="1">
-        <v>51.6</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1908,19 +1908,19 @@
         <v>3</v>
       </c>
       <c r="I7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7">
         <v>7</v>
       </c>
       <c r="M7">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N7">
         <v>95</v>
@@ -2002,34 +2002,34 @@
         <v>5</v>
       </c>
       <c r="G9">
+        <v>5</v>
+      </c>
+      <c r="H9">
+        <v>7</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
         <v>6</v>
       </c>
-      <c r="H9">
-        <v>5</v>
-      </c>
-      <c r="I9">
-        <v>3</v>
-      </c>
-      <c r="J9">
-        <v>8</v>
-      </c>
       <c r="K9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M9">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="N9">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="O9">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P9" s="1">
-        <v>32.8</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2049,34 +2049,34 @@
         <v>8</v>
       </c>
       <c r="G10">
+        <v>9</v>
+      </c>
+      <c r="H10">
         <v>10</v>
       </c>
-      <c r="H10">
-        <v>8</v>
-      </c>
       <c r="I10">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J10">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K10">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L10">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M10">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="N10">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="O10">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="P10" s="1">
-        <v>25.2</v>
+        <v>24.9</v>
       </c>
     </row>
   </sheetData>
@@ -2450,13 +2450,13 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K8">
         <v>4</v>
       </c>
       <c r="L8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M8">
         <v>1</v>
@@ -2632,19 +2632,19 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M12">
         <v>24</v>
@@ -3052,31 +3052,31 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21">
         <v>2</v>
       </c>
       <c r="J21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K21">
         <v>5</v>
       </c>
       <c r="L21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M21">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="N21">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="O21" s="1">
-        <v>72.40000000000001</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="22" spans="1:15">
@@ -3143,10 +3143,10 @@
         <v>2</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -3205,10 +3205,10 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M24">
         <v>6</v>
@@ -3290,19 +3290,19 @@
         <v>1</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K26">
         <v>3</v>
       </c>
       <c r="L26">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M26">
         <v>18</v>
@@ -4237,7 +4237,7 @@
         <v>4</v>
       </c>
       <c r="E21">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F21" s="1">
         <v>10.3</v>
@@ -4246,7 +4246,7 @@
         <v>13.8</v>
       </c>
       <c r="H21" s="1">
-        <v>27.6</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="22" spans="1:8">
